--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484702_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484702_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0589</v>
+        <v>0.5131</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2048</v>
+        <v>3.6034</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.2638</v>
+        <v>-3.0903</v>
       </c>
       <c r="G3" t="n">
         <v>2.2155</v>
@@ -688,13 +688,13 @@
         <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5518</v>
+        <v>-0.9798</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.101</v>
+        <v>-0.7025</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4508</v>
+        <v>-0.2774</v>
       </c>
       <c r="V3" t="n">
         <v>0.0104</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.406</v>
+        <v>-0.3376</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5481</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-1.078</v>
       </c>
       <c r="G4" t="n">
         <v>-1.7298</v>
@@ -766,13 +766,13 @@
         <v>0.3665</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6316000000000001</v>
+        <v>-0.5632</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6606</v>
+        <v>-0.4683</v>
       </c>
       <c r="U4" t="n">
-        <v>0.029</v>
+        <v>-0.0948</v>
       </c>
       <c r="V4" t="n">
         <v>1.5889</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4339</v>
+        <v>-0.3596</v>
       </c>
       <c r="E5" t="n">
         <v>-0.9127</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4788</v>
+        <v>0.5531</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8682</v>
@@ -844,13 +844,13 @@
         <v>0.1833</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1888</v>
+        <v>-0.1144</v>
       </c>
       <c r="T5" t="n">
         <v>-0.1101</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0043</v>
       </c>
       <c r="V5" t="n">
         <v>0.6231</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. JURADO TRAVER</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4979</v>
+        <v>-0.869</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.9032</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4973</v>
+        <v>-1.7722</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8412</v>
+        <v>0.4476</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8347</v>
+        <v>-0.0074</v>
       </c>
       <c r="I6" t="n">
-        <v>1.0065</v>
+        <v>0.4549</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5666</v>
+        <v>1.3897</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8482</v>
+        <v>1.223</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7183</v>
+        <v>0.1667</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.9421</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0136</v>
+        <v>-1.2303</v>
       </c>
       <c r="O6" t="n">
         <v>0.2882</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3823</v>
+        <v>0.1833</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9321</v>
+        <v>-0.1833</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5498</v>
+        <v>0.3665</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3548</v>
+        <v>-0.2329</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6765</v>
+        <v>-0.3032</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3217</v>
+        <v>0.0703</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3115</v>
+        <v>-1.267</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>L. JURADO TRAVER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0365</v>
+        <v>-0.8708</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7109</v>
+        <v>-0.7698</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7475</v>
+        <v>-0.1009</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4476</v>
+        <v>1.8412</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0074</v>
+        <v>0.8347</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4549</v>
+        <v>1.0065</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3897</v>
+        <v>2.5666</v>
       </c>
       <c r="K7" t="n">
-        <v>1.223</v>
+        <v>1.8482</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1667</v>
+        <v>0.7183</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9421</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2303</v>
+        <v>-1.0136</v>
       </c>
       <c r="O7" t="n">
         <v>0.2882</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1833</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1833</v>
+        <v>-2.9321</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4004</v>
+        <v>-0.0181</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4955</v>
+        <v>-0.0927</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0951</v>
+        <v>0.0746</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.267</v>
+        <v>-0.3115</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5045</v>
+        <v>-1.0426</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7985</v>
+        <v>-0.51</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.706</v>
+        <v>-0.5326</v>
       </c>
       <c r="G8" t="n">
         <v>0.8535</v>
@@ -1078,13 +1078,13 @@
         <v>0.5498</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8919</v>
+        <v>-0.4301</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.4823</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1212</v>
+        <v>0.0522</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0812</v>
+        <v>-1.9326</v>
       </c>
       <c r="E9" t="n">
         <v>-2.0094</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0718</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G9" t="n">
         <v>0.0738</v>
@@ -1156,13 +1156,13 @@
         <v>0.1833</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5057</v>
+        <v>-0.3571</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2202</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2855</v>
+        <v>-0.1369</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.243</v>
+        <v>-2.3122</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6222</v>
+        <v>-1.3198</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6208</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9447</v>
@@ -1234,13 +1234,13 @@
         <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.649</v>
+        <v>-0.7181</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2111</v>
+        <v>-0.9087</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5622</v>
+        <v>0.1906</v>
       </c>
       <c r="V10" t="n">
         <v>0.6335</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.28</v>
+        <v>-2.3244</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5705</v>
+        <v>-0.2681</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7095</v>
+        <v>-2.0563</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5661</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7425</v>
+        <v>-0.787</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.101</v>
+        <v>-0.7986</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3585</v>
+        <v>0.0117</v>
       </c>
       <c r="V11" t="n">
         <v>0.945</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3516</v>
+        <v>-4.6538</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1344</v>
+        <v>-2.3128</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2172</v>
+        <v>-2.341</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9763</v>
@@ -1390,13 +1390,13 @@
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.247</v>
+        <v>-0.5492</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3499</v>
+        <v>-0.5283</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1029</v>
+        <v>-0.021</v>
       </c>
       <c r="V12" t="n">
         <v>-0.945</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5975</v>
+        <v>-5.7511</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5929</v>
+        <v>-3.7712</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0046</v>
+        <v>-1.9799</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4415</v>
@@ -1468,13 +1468,13 @@
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4963</v>
+        <v>-0.6499</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6252</v>
+        <v>-0.8035</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1289</v>
+        <v>0.1536</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6439</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.5408</v>
+        <v>-18.9904</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.2272</v>
+        <v>-5.6766</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.3138</v>
+        <v>-13.3137</v>
       </c>
       <c r="G14" t="n">
         <v>-4.1448</v>
@@ -1546,13 +1546,13 @@
         <v>7.330299999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.9502</v>
+        <v>-5.399799999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.9688</v>
+        <v>-5.418399999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01870000000000009</v>
+        <v>0.01860000000000006</v>
       </c>
       <c r="V14" t="n">
         <v>0.6335000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.7515</v>
+        <v>11.361</v>
       </c>
       <c r="E15" t="n">
-        <v>10.8793</v>
+        <v>10.687</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8721</v>
+        <v>0.674</v>
       </c>
       <c r="G15" t="n">
         <v>8.273400000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.6493</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5172</v>
+        <v>1.1267</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6946</v>
+        <v>0.5023</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8226</v>
+        <v>0.6244</v>
       </c>
       <c r="V15" t="n">
         <v>0.3115</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3493</v>
+        <v>3.258</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1348</v>
+        <v>3.3655</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2145</v>
+        <v>-0.1075</v>
       </c>
       <c r="G16" t="n">
         <v>0.797</v>
@@ -1702,13 +1702,13 @@
         <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0025</v>
+        <v>0.9112</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9872</v>
+        <v>0.218</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0153</v>
+        <v>0.6932</v>
       </c>
       <c r="V16" t="n">
         <v>0.6335</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.9847</v>
+        <v>3.1571</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3306</v>
+        <v>1.8498</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6541</v>
+        <v>1.3073</v>
       </c>
       <c r="G17" t="n">
         <v>1.8878</v>
@@ -1780,13 +1780,13 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0968</v>
+        <v>1.2692</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9698</v>
+        <v>0.4891</v>
       </c>
       <c r="U17" t="n">
-        <v>1.127</v>
+        <v>0.7801</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7705</v>
+        <v>2.6525</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4889</v>
+        <v>1.2966</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2817</v>
+        <v>1.356</v>
       </c>
       <c r="G18" t="n">
         <v>0.6411</v>
@@ -1858,13 +1858,13 @@
         <v>2.0158</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7079</v>
+        <v>0.5899</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3643</v>
+        <v>0.172</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3437</v>
+        <v>0.418</v>
       </c>
       <c r="V18" t="n">
         <v>0.3219</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MARIA VENTURA</t>
+          <t>A. CEJUDO GALAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8875</v>
+        <v>2.315</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0025</v>
+        <v>1.5503</v>
       </c>
       <c r="F19" t="n">
-        <v>1.89</v>
+        <v>0.7647</v>
       </c>
       <c r="G19" t="n">
-        <v>0.011</v>
+        <v>0.3821</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9371</v>
+        <v>2.2412</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9261</v>
+        <v>-1.8591</v>
       </c>
       <c r="J19" t="n">
-        <v>0.054</v>
+        <v>1.5789</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6594</v>
+        <v>2.861</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6054</v>
+        <v>-1.2821</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.043</v>
+        <v>-1.1968</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2777</v>
+        <v>-0.6198</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3207</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="P19" t="n">
         <v>1.6493</v>
@@ -1936,28 +1936,28 @@
         <v>1.6493</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2376</v>
+        <v>0.2836</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0565</v>
+        <v>-0.0286</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2941</v>
+        <v>0.3122</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALAN</t>
+          <t>M. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5399</v>
+        <v>2.2314</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9734</v>
+        <v>0.0936</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5665</v>
+        <v>2.1378</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3821</v>
+        <v>0.011</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2412</v>
+        <v>0.9371</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8591</v>
+        <v>-0.9261</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5789</v>
+        <v>0.054</v>
       </c>
       <c r="K20" t="n">
-        <v>2.861</v>
+        <v>0.6594</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2821</v>
+        <v>-0.6054</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1968</v>
+        <v>-0.043</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6198</v>
+        <v>0.2777</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5770999999999999</v>
+        <v>-0.3207</v>
       </c>
       <c r="P20" t="n">
         <v>1.6493</v>
@@ -2014,22 +2014,22 @@
         <v>1.6493</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4915</v>
+        <v>0.5815</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6056</v>
+        <v>0.0396</v>
       </c>
       <c r="U20" t="n">
-        <v>0.114</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="21">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3827</v>
+        <v>0.5532</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5729</v>
+        <v>1.669</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1901</v>
+        <v>-1.1158</v>
       </c>
       <c r="G23" t="n">
         <v>1.2525</v>
@@ -2248,13 +2248,13 @@
         <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>0.214</v>
+        <v>0.3844</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1297</v>
+        <v>-0.0335</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3437</v>
+        <v>0.418</v>
       </c>
       <c r="V23" t="n">
         <v>-1.267</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4363</v>
+        <v>-0.0488</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1741</v>
+        <v>0.1143</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2622</v>
+        <v>-0.1631</v>
       </c>
       <c r="G24" t="n">
         <v>-1.9126</v>
@@ -2326,13 +2326,13 @@
         <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0103</v>
+        <v>0.3978</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3499</v>
+        <v>-0.0614</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3602</v>
+        <v>0.4593</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.2323</v>
+        <v>-1.1114</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4325</v>
+        <v>-1.3364</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2002</v>
+        <v>0.225</v>
       </c>
       <c r="G25" t="n">
         <v>-0.3665</v>
@@ -2404,13 +2404,13 @@
         <v>0.3665</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0346</v>
+        <v>0.1555</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2572</v>
+        <v>-0.161</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2918</v>
+        <v>0.3165</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>V. RODRIGUEZ GIL</t>
+          <t>A. PEREZ RIPOLL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.8827</v>
+        <v>-1.7152</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3134</v>
+        <v>-2.4159</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4307</v>
+        <v>0.7007</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.595</v>
+        <v>-2.8191</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.1686</v>
+        <v>-0.2836</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.4265</v>
+        <v>-2.5355</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.4362</v>
+        <v>-1.9747</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3625</v>
+        <v>-0.1767</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.0737</v>
+        <v>-1.7981</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.1588</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.806</v>
+        <v>-0.1069</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3528</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.3665</v>
+        <v>1.0995</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.3823</v>
+        <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>0.435</v>
+        <v>0.0043</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0392</v>
+        <v>-0.4412</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4742</v>
+        <v>0.4455</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A. PEREZ RIPOLL</t>
+          <t>V. RODRIGUEZ GIL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.0255</v>
+        <v>-2.1216</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.8005</v>
+        <v>-2.6019</v>
       </c>
       <c r="F27" t="n">
-        <v>0.775</v>
+        <v>0.4803</v>
       </c>
       <c r="G27" t="n">
-        <v>-2.8191</v>
+        <v>-2.595</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2836</v>
+        <v>-1.1686</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.5355</v>
+        <v>-1.4265</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.9747</v>
+        <v>-1.4362</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.1767</v>
+        <v>-0.3625</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.7981</v>
+        <v>-1.0737</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-1.1588</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.1069</v>
+        <v>-0.806</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.7374000000000001</v>
+        <v>-0.3528</v>
       </c>
       <c r="P27" t="n">
-        <v>1.0995</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R27" t="n">
-        <v>1.0995</v>
+        <v>2.3823</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.306</v>
+        <v>0.1961</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.8258</v>
+        <v>-0.3276</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5198</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.4742</v>
+        <v>-2.9161</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.2686</v>
+        <v>-2.884</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2055</v>
+        <v>-0.0321</v>
       </c>
       <c r="G28" t="n">
         <v>-3.3326</v>
@@ -2638,13 +2638,13 @@
         <v>1.2828</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.5081</v>
+        <v>0.05</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.3861</v>
       </c>
       <c r="U28" t="n">
-        <v>0.2627</v>
+        <v>0.4361</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2674,10 +2674,10 @@
         <v>19.5406</v>
       </c>
       <c r="E29" t="n">
-        <v>13.3138</v>
+        <v>13.31339999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>6.227</v>
+        <v>6.2273</v>
       </c>
       <c r="G29" t="n">
         <v>4.144600000000001</v>
@@ -2695,16 +2695,16 @@
         <v>18.6071</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.7219</v>
+        <v>-2.721900000000001</v>
       </c>
       <c r="M29" t="n">
         <v>-11.7405</v>
       </c>
       <c r="N29" t="n">
-        <v>-6.289600000000001</v>
+        <v>-6.2896</v>
       </c>
       <c r="O29" t="n">
-        <v>-5.4509</v>
+        <v>-5.450900000000001</v>
       </c>
       <c r="P29" t="n">
         <v>10.0791</v>
@@ -2716,13 +2716,13 @@
         <v>17.4093</v>
       </c>
       <c r="S29" t="n">
-        <v>5.950300000000001</v>
+        <v>5.950200000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.01869999999999994</v>
+        <v>-0.01840000000000019</v>
       </c>
       <c r="U29" t="n">
-        <v>5.9691</v>
+        <v>5.968799999999999</v>
       </c>
       <c r="V29" t="n">
         <v>-0.6335999999999998</v>
